--- a/test_dir/example_workbook_result.xlsx
+++ b/test_dir/example_workbook_result.xlsx
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.01684880256652832</v>
+        <v>0.0160059928894043</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>{"quotaName": "\u5f00\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 2}</t>
+          <t>{"quotaName": "\u5f00\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 1}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '开盘价', 'quotaType': 'STOCK', 'quotaValue': 2}}</t>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '开盘价', 'quotaType': 'STOCK', 'quotaValue': 1}}</t>
         </is>
       </c>
     </row>
@@ -1140,19 +1140,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01200008392333984</v>
+        <v>0.01100635528564453</v>
       </c>
       <c r="E3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>{"quotaName": "\u6536\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 8}</t>
+          <t>{"quotaName": "\u6536\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 9}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '收盘价', 'quotaType': 'STOCK', 'quotaValue': 8}}</t>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '收盘价', 'quotaType': 'STOCK', 'quotaValue': 9}}</t>
         </is>
       </c>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01200008392333984</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
+        <v>0.01100635528564453</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{"quotaName": "\u6210\u4ea4\u91cf", "quotaType": "STOCK", "quotaValue": 1}</t>
+          <t>{"quotaName": "\u6210\u4ea4\u91cf", "quotaType": "STOCK", "quotaValue": 7}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '成交量', 'quotaType': 'STOCK', 'quotaValue': 1}}</t>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '成交量', 'quotaType': 'STOCK', 'quotaValue': 7}}</t>
         </is>
       </c>
     </row>
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.007965326309204102</v>
-      </c>
-      <c r="E5" s="2" t="b">
-        <v>1</v>
+        <v>0.003000736236572266</v>
+      </c>
+      <c r="E5" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{"quotaName": "\u57fa\u91d1\u51c0\u503c", "quotaType": "FUND", "quotaValue": 127}</t>
+          <t>{"quotaName": "\u57fa\u91d1\u51c0\u503c", "quotaType": "FUND", "quotaValue": 1}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金净值', 'quotaType': 'FUND', 'quotaValue': 127}}</t>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金净值', 'quotaType': 'FUND', 'quotaValue': 1}}</t>
         </is>
       </c>
     </row>
@@ -1239,19 +1239,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.006000280380249023</v>
+        <v>0.003000736236572266</v>
       </c>
       <c r="E6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{"quotaName": "\u57fa\u91d1\u89c4\u6a21", "quotaType": "FUND", "quotaValue": 113}</t>
+          <t>{"quotaName": "\u57fa\u91d1\u89c4\u6a21", "quotaType": "FUND", "quotaValue": 9}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金规模', 'quotaType': 'FUND', 'quotaValue': 113}}</t>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金规模', 'quotaType': 'FUND', 'quotaValue': 9}}</t>
         </is>
       </c>
     </row>

--- a/test_dir/example_workbook_result.xlsx
+++ b/test_dir/example_workbook_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27330" windowHeight="15375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28935" windowHeight="15930" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,14 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -176,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +178,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFB6C1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -371,12 +376,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFB6C1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
   </fills>
@@ -488,86 +493,80 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
@@ -576,10 +575,10 @@
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
@@ -588,10 +587,10 @@
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
@@ -600,10 +599,10 @@
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
@@ -612,10 +611,10 @@
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
@@ -624,20 +623,28 @@
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1050,8 +1057,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="0"/>
+  <cols>
+    <col width="4.375" customWidth="1" min="1" max="1"/>
+    <col width="8.875" customWidth="1" min="2" max="2"/>
+    <col width="5.125" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1076,15 +1088,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>跑批是否成功</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>跑批结果是否符合预期</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>跑批响应格式化后结果</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>跑批响应原始结果</t>
         </is>
@@ -1107,19 +1124,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0160059928894043</v>
-      </c>
-      <c r="E2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{"quotaName": "\u5f00\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 1}</t>
-        </is>
+        <v>0.01020479202270508</v>
+      </c>
+      <c r="E2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '开盘价', 'quotaType': 'STOCK', 'quotaValue': 1}}</t>
+          <t>{"quotaName": "\u5f00\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 9}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '开盘价', 'quotaType': 'STOCK', 'quotaValue': 9}}</t>
         </is>
       </c>
     </row>
@@ -1140,19 +1160,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01100635528564453</v>
-      </c>
-      <c r="E3" s="2" t="b">
+        <v>0.008000850677490229</v>
+      </c>
+      <c r="E3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>{"quotaName": "\u6536\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 9}</t>
-        </is>
+      <c r="F3" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '收盘价', 'quotaType': 'STOCK', 'quotaValue': 9}}</t>
+          <t>{"quotaName": "\u6536\u76d8\u4ef7", "quotaType": "STOCK", "quotaValue": 7}</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '收盘价', 'quotaType': 'STOCK', 'quotaValue': 7}}</t>
         </is>
       </c>
     </row>
@@ -1173,19 +1196,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01100635528564453</v>
-      </c>
-      <c r="E4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>{"quotaName": "\u6210\u4ea4\u91cf", "quotaType": "STOCK", "quotaValue": 7}</t>
-        </is>
+        <v>0.006016731262207031</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '成交量', 'quotaType': 'STOCK', 'quotaValue': 7}}</t>
+          <t>{"quotaName": "\u6210\u4ea4\u91cf", "quotaType": "STOCK", "quotaValue": 1}</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '成交量', 'quotaType': 'STOCK', 'quotaValue': 1}}</t>
         </is>
       </c>
     </row>
@@ -1206,19 +1232,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.003000736236572266</v>
-      </c>
-      <c r="E5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>{"quotaName": "\u57fa\u91d1\u51c0\u503c", "quotaType": "FUND", "quotaValue": 1}</t>
-        </is>
+        <v>0.00200104713439941</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金净值', 'quotaType': 'FUND', 'quotaValue': 1}}</t>
+          <t>{"quotaName": "\u57fa\u91d1\u51c0\u503c", "quotaType": "FUND", "quotaValue": 148}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金净值', 'quotaType': 'FUND', 'quotaValue': 148}}</t>
         </is>
       </c>
     </row>
@@ -1239,19 +1268,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.003000736236572266</v>
-      </c>
-      <c r="E6" s="2" t="b">
+        <v>0.00200104713439941</v>
+      </c>
+      <c r="E6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>{"quotaName": "\u57fa\u91d1\u89c4\u6a21", "quotaType": "FUND", "quotaValue": 9}</t>
-        </is>
+      <c r="F6" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金规模', 'quotaType': 'FUND', 'quotaValue': 9}}</t>
+          <t>{"quotaName": "\u57fa\u91d1\u89c4\u6a21", "quotaType": "FUND", "quotaValue": 191}</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>{'msg': '操作成功', 'code': 200, 'data': {'quotaName': '基金规模', 'quotaType': 'FUND', 'quotaValue': 191}}</t>
         </is>
       </c>
     </row>
